--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260630.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>159,675</t>
+          <t>157,755</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.09%</t>
+          <t>26.23%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>18,275</t>
+          <t>18,055</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>9.33%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>115,830</t>
+          <t>58,375</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.65%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>59,085</t>
+          <t>114,440</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.38%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>140,655</t>
+          <t>138,965</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>75,875</t>
+          <t>74,965</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>68,880</t>
+          <t>68,050</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>52,335</t>
+          <t>51,705</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,895</t>
+          <t>22,625</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,183</t>
+          <t>20,933</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,530</t>
+          <t>36,090</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>23,545</t>
+          <t>9,190</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>23,265</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>59,155</t>
+          <t>58,445</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -941,78 +941,78 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>89,195</t>
+          <t>88,125</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>22,600</t>
+          <t>13,451</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,798</t>
+          <t>22,330</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>30,428</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>41,980</t>
+          <t>41,480</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1051,34 +1051,34 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>68,868</t>
+          <t>68,038</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>89,066,453</t>
+          <t>11,066</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,738</t>
+          <t>24,438</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>11,196</t>
+          <t>83,936,823</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,455</t>
+          <t>21,195</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>147,015</t>
+          <t>145,255</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,867</t>
+          <t>22,597</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,521</t>
+          <t>18,301</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,665</t>
+          <t>13,505</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,480</t>
+          <t>42,960</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>50,090</t>
+          <t>49,490</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>942,745</t>
+          <t>1,049,661</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>63,686,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2,642,358</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
